--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,654 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Robert Sutton</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/bobsutton1/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>@work_matters</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>The No Asshole Rule author</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kim Scott</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Radical Candor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kimm4/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>@kimballscott</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@kimmalonescott</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Radical Candor author</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amy Edmondson</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Harvard Business School</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>@AmyCEdmondson</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>@amycedmondson.bsky.social</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Psychological safety researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Simon Sinek</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/simonsinek/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>@simonsinek</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@simonsinek</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Simon Sinek</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Start With Why author</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Patrick Lencioni</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The Table Group</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/patrick-lencioni-orghealth/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>@patricklencioni</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>@patricklencioniofficial</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>@PatrickLencioniOfficial</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Working Genius, Five Dysfunctions author</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Liz Wiseman</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Wiseman Group</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/lizwiseman</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>@LizWiseman</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>@bylizwiseman</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Multipliers author</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tessa West</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NYU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/tessa-west-129b51131/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>@TessaWestNYU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Jerks at Work author</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Adam Grant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wharton</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/adammgrant/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>@AdamMGrant</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>@adamgrant</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>@adamgrant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Give and Take author</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dave Bailey</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO Coach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/davesuperman/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>@davesuperman</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CEO coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kathryn Landis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Executive Coach</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kathrynlandis/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Executive coach, LinkedIn active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tim Duggan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/timduggan1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>@tim_duggan</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Australian workplace culture author</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Achim Nowak</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Executive Coach</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/achimnowak/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>@AchimNowak</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Executive coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Reed Hastings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/reedhastings</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>@reedhastings</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Netflix co-founder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,6 @@
           <t>@work_matters</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -594,11 +588,6 @@
           <t>@kimmalonescott</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -631,22 +620,16 @@
           <t>Harvard Business School</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>@AmyCEdmondson</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>@amycedmondson.bsky.social</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -674,7 +657,6 @@
           <t>Simon Sinek</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>linkedin.com/in/simonsinek/</t>
@@ -690,15 +672,11 @@
           <t>@simonsinek</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Simon Sinek</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -746,15 +724,11 @@
           <t>@patricklencioniofficial</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>@PatrickLencioniOfficial</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -802,11 +776,6 @@
           <t>@bylizwiseman</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -849,12 +818,6 @@
           <t>@TessaWestNYU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -902,15 +865,11 @@
           <t>@adamgrant</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>@adamgrant</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -953,12 +912,6 @@
           <t>@davesuperman</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -996,13 +949,6 @@
           <t>linkedin.com/in/kathrynlandis/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -1040,17 +986,11 @@
           <t>linkedin.com/in/timduggan1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>@tim_duggan</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -1093,12 +1033,6 @@
           <t>@AchimNowak</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -1141,12 +1075,6 @@
           <t>@reedhastings</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>2026-03-24</t>
@@ -1165,6 +1093,166 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>Netflix co-founder</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brene Brown</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Researcher/Author</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/brenebrown/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>@BreneBrown</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>@brenebrown</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>@brenebrown</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>facebook.com/brenebrown/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Dare to Lead author, researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chartered Management Institute</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Professional Body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>@cmi_managers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>facebook.com/bettermanagers/</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UK professional body for management</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gallup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Research Organization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>linkedin.com/company/gallup</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>@Gallup</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>facebook.com/gallup/</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Engagement research organization</t>
         </is>
       </c>
     </row>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1127,9 +1127,6 @@
           <t>@brenebrown</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>facebook.com/brenebrown/</t>
@@ -1167,17 +1164,11 @@
           <t>Professional Body</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>@cmi_managers</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>facebook.com/bettermanagers/</t>
@@ -1225,11 +1216,6 @@
           <t>@Gallup</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>facebook.com/gallup/</t>
@@ -1253,6 +1239,770 @@
       <c r="N17" t="inlineStr">
         <is>
           <t>Engagement research organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Richard Ingersoll</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>University of Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>richard-ingersoll-40851717</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Teacher turnover researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Linda Darling-Hammond</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Learning Policy Institute</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>linda-darling-hammond-885401193</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>@LDH_ed</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Learning Policy Institute founder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andy Hargreaves</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Boston College</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>@HargreavesBC</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Teacher professionalism researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Michael Fullan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>@MichaelFullan1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>School change researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Viviane Robinson</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>University of Auckland</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>viviane-robinson-7152212b</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>@RobinsonViviane</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Education leadership researcher, NZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Elena Aguilar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bright Morning Consulting</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>elena-aguilar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>@brightmorningtm</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>@brightmorningtm</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Art of Coaching author</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Todd Whitaker</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>University of Missouri</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>@ToddWhitaker</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>@toddwhitaker.bsky.social</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Principal-teacher relationship author</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chase Mielke</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>chase-mielke</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>@chasemielke</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>@chasemielke</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>chasemielkespeaker</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Burnout Cure author</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jack Worth</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NFER</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jack-worth-1842285a</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>@JackWorthNFER</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>NFER teacher labour market researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>David Rock</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NeuroLeadership Institute</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dr-david-rock</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>@davidrock101</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SCARF model creator</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RAND Corporation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Research Organization</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rand-corporation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>@RANDCorporation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@randcorporation</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>@rand.org</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>RANDCorporation</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Research organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Learning Policy Institute</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Research Organization</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>learning-policy-institute</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>@LPI_Learning</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>LearningPolicyInstitute</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Education policy research</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OECD Education</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>International Organization</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>@OECDEduSkills</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>OECD education division</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ASCD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Professional Organization</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ascd</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>@ASCD</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>@officialascd</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ascd.org</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Education professional body</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WeAreTeachers</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Media Organization</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>weareteachers</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>@WeAreTeachers</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>@weareteachers</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>WeAreTeachers</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Teacher media platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NFER</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Research Organization</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>thenfer</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>@TheNFER</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>TheNFER</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>UK education research foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>McKell Institute</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Think Tank</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>the-mckell-institute</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>@McKellInstitute</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>@mckellinstitute</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mckellinstitute</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Australian policy think tank</t>
         </is>
       </c>
     </row>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2006,6 +2006,713 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Herminia Ibarra</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>London Business School</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>herminia-ibarra-4455411a</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>@HerminiaIbarra</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Leadership identity researcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Liz Fosslien</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>liz-fosslien</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>@fosslien</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@lizfosslien</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No Hard Feelings co-author</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Julie Zhuo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Author/Product</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>julie-zhuo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>@joulee</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@joulee</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>The Making of a Manager author</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Michael Bungay Stanier</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Box of Crayons</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>michaelbungaystanier</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>@mbs_works</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>The Coaching Habit author</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Marshall Goldsmith</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Executive Coach</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>marshallgoldsmith</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>@coachgoldsmith</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>@marshall_goldsmith</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Marshall Goldsmith</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Marshall.Goldsmith.Library</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>What Got You Here author</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Linda A. Hill</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Harvard Business School</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>linda-hill-hbs</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>@Linda_A_Hill</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Becoming a Manager author</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ram Charan</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Business Consultant</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rcharan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>@DrRam_Charan</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Leadership Pipeline co-author</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ronald Heifetz</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Harvard Kennedy School</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>@RonHeifetz</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Adaptive leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Justin Bariso</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>justinbariso</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>@JustinJBariso</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>EQ writer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sara Canaday</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Leadership Dev</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>saracanaday</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>@saracanaday</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>@saracanaday</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CanadayandAssociates</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Leadership transitions expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rachel Pacheco</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>rachel-pacheco</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>@rachelpacheco</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>@rachel.pacheco</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Bringing Up the Boss author</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tessa Brock</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Leadership Consultant</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>tessa-brock-125455174</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Grief of new leader writer</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Glenn Birkelev</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Leadership Content</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>glenn-birkelev-1395405</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Leadership transition content</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RHR International</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>rhr-international</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>@RHRIntlLLP</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>CEO loneliness research</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>kpmg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>@kpmg</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>@kpmg</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>facebook.com/KPMG</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Imposter syndrome study</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Wharton Executive Education</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Business School</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wharton-executive-education</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>facebook.com/whartonexeced</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>New manager failure rate research</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2713,6 +2713,442 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jeff Bezos</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>@JeffBezos</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>@jeffbezos</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>No LinkedIn profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Daniel Pink</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/danielpink</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>@DanielPink</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>@danielpink</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>@danielhpink</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Columbia Business School</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Business School</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>columbia-business-school</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>@Columbia_Biz</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>@columbia_biz</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>@columbia_biz</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>@columbia_biz</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>@columbiabusiness.bsky.social</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>facebook.com/columbiabusiness</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Harvard Business School</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Business School</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>harvard-business-school</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>@HarvardHBS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>@harvardhbs</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>@harvardhbs</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>@harvardhbs</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>@harvardhbs.bsky.social</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>facebook.com/harvardbusinessschool</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>deloitte</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>@Deloitte</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>@deloitte</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>@deloitte</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>facebook.com/deloitte</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mckinsey</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>@McKinsey</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bain-and-company</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>@BainandCompany</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>@bainandcompany</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>facebook.com/bainandcompany</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>@Amazon</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>@amazon</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>@amazon</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>facebook.com/Amazon</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -2724,7 +2724,6 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>@JeffBezos</t>
@@ -2735,11 +2734,6 @@
           <t>@jeffbezos</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -2787,15 +2781,11 @@
           <t>@danielpink</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>@danielhpink</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -2811,7 +2801,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2859,7 +2848,6 @@
           <t>facebook.com/columbiabusiness</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -2875,7 +2863,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2923,7 +2910,6 @@
           <t>facebook.com/harvardbusinessschool</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -2939,7 +2925,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2972,14 +2957,11 @@
           <t>@deloitte</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>facebook.com/deloitte</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -2995,7 +2977,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3018,12 +2999,6 @@
           <t>@McKinsey</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3039,7 +3014,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3067,15 +3041,11 @@
           <t>@bainandcompany</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>facebook.com/bainandcompany</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3091,7 +3061,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3119,19 +3088,16 @@
           <t>@amazon</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>@amazon</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>facebook.com/Amazon</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3147,7 +3113,6 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3114,6 +3114,330 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Christopher M. Barnes</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>@chris24barnes</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Sleep &amp; leadership researcher. X handle LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dr. Els van der Helm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>@elsonsleep</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>@drelsvanderhelm</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Sleep neuroscientist. Handles LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dr. Sophie Bostock</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>@drsophiebostock</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>@drsophiebostock</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>@drsophiebostock</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>@drsophiebostock</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Sleep scientist. Handles LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Matthew Walker</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>@sleepdiplomat</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>@drmattwalker</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>@sleepdiplomat</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>@sleepdiplomat</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>@sleepdiplomat</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Neuroscientist, Why We Sleep author. VERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dr. Shelby Harris</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>@SleepDocShelby</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>@SleepDocShelby</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>@sleepdocshelby</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Behavioral sleep medicine. VERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Arianna Huffington</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Thrive Global</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>@ariannahuff</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>@ariannahuff</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>@ariannahuff</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Arianna Huffington</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>@ariannahuff.bsky.social</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>AriannaHuffington</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Thrive Global founder. VERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Nick Littlehales</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>@SportSleepCoach</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>@sportsleepcoach</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>@sportsleepcoach</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>sportsleepcoach</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Elite sport sleep coach. R90 method. LIKELY.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3438,6 +3438,236 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chester Elton</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>@chesterelton</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>@chesterelton</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - author of Leading with Gratitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ed Batista</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>@edbatista</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - executive coach, Stanford lecturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Vivek Murthy</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>@vivabornerthy</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - former US Surgeon General, loneliness epidemic</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Julianne Holt-Lunstad</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>@jholtlunstad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - BYU researcher on social connections and health</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Nick Jonsson</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - author of Executive Loneliness</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Morra Aarons-Mele</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - author of The Anxious Achiever</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jerry Colonna</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Leadership loneliness blog - CEO coach, author of Reboot</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3444,7 +3444,6 @@
           <t>Chester Elton</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>@chesterelton</t>
@@ -3455,11 +3454,6 @@
           <t>@chesterelton</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3482,18 +3476,11 @@
           <t>Ed Batista</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>@edbatista</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3516,18 +3503,11 @@
           <t>Vivek Murthy</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>@vivabornerthy</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3550,18 +3530,11 @@
           <t>Julianne Holt-Lunstad</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>@jholtlunstad</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3584,14 +3557,6 @@
           <t>Nick Jonsson</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3614,14 +3579,6 @@
           <t>Morra Aarons-Mele</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3644,14 +3601,6 @@
           <t>Jerry Colonna</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>2026-03-25</t>
@@ -3665,6 +3614,176 @@
       <c r="L72" t="inlineStr">
         <is>
           <t>Leadership loneliness blog - CEO coach, author of Reboot</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Henry Cloud</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Boundaries/DrCloud.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>@DrHenryCloud</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DrHenryCloud</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Boundaries author</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>John Townsend</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Townsend Institute</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>@drjohntownsend</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Boundaries co-author</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tania Singer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Max Planck Institute</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>INACTIVE</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Neuroscience researcher, minimal social media</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>David Morrison</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Retired Australian Army</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>INACTIVE</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Former Australian Army Chief, no social accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Edwin Friedman</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>DECEASED</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Died 1996. Family systems leadership author.</t>
         </is>
       </c>
     </row>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3787,6 +3787,130 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Craig Groeschel</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Life.Church</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>craig-groeschel-11463a112</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>@craiggroeschel</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>@craiggroeschel</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>@craiggroeschel</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>@craiggroeschel</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>@craiggroeschel</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>craiggroeschel</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Founder Life.Church. Threads LIKELY. X possibly inactive. Bluesky NOT FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Life.Church</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Life.Church</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>@life.church</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>@lifechurch</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>@life.church</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>life.church</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Church org. Tagged on IG and FB.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3911,6 +3911,80 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ASBA Limited</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ASBA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ASBALtd</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Peak body for independent school business managers in Australia/NZ. CEO: Kathy Dickson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Kathy Dickson</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ASBA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/kathy-dickson</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>CEO of ASBA. LinkedIn only (personal profile, cannot tag via API).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3985,6 +3985,105 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jocko Willink</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Echelon Front</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>@jockowillink</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>@jockowillink</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>@jocko_willink</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Jocko Willink</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Jocko Willink</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Extreme Ownership co-author, Navy SEAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Leif Babin</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Echelon Front</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/leif-babin-2a43b631/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>@leifbabin</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Extreme Ownership co-author, Navy SEAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4084,6 +4084,48 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ryan Hawk</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ryanhawk12</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>@RyanHawk12</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>@ryanhawk12</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>TheLearningLeaderShow</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Podcast host, author, speaker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4126,6 +4129,39 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Edward Amey</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Jay Nolan Community Services</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>edward-r-amey-ms-5280aa5</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>CEO Jay Nolan Community Services. LinkedIn verified. No other social media found.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4162,6 +4162,48 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Crucial Learning (VitalSmarts)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Crucial Learning</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>company/crucial-learning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>@VitalSmarts</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Publishers of Crucial Conversations. Formerly VitalSmarts.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4204,6 +4204,63 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>James Clear</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Author / Speaker</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>@JamesClear</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>@jamesclear</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>@jamesclear</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>@jamesclear</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>@JamesClear</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Atomic Habits author. 20M+ copies sold.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4261,6 +4261,65 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>John Maxwell</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>The John Maxwell Company</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>johncmaxwell</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>@JohnCMaxwell</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>@johncmaxwell</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@johncmaxwell</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>johnmaxwell</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Major leadership figure. X/Twitter and Instagram verified. No confirmed Bluesky or Threads.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -4292,13 +4292,11 @@
           <t>@johncmaxwell</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>johnmaxwell</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>2026-03-27</t>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4318,6 +4318,48 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Dave Stachowiak</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Host, Coaching for Leaders podcast</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Coaching for Leaders</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>davestachowiak</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>@davestachowiak</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X: VERIFIED, LinkedIn: VERIFIED. No IG/TikTok/YT/Threads/Bluesky found.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4360,6 +4360,43 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ian Cumming</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SU Australia</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ian-cumming-gaicd-157b885b</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GAICD, Group Director Operations, MBA. Only LinkedIn found.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/carousel-workflow/handle-database.xlsx
+++ b/data/carousel-workflow/handle-database.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4397,6 +4397,82 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>David Ashcraft</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Global Leadership Network</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GLS Podcast host</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Whitney Putnam</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Global Leadership Network</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>@glnsummit</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>@glnsummit</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>@glnsummit</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Global Leadership Network</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GLS Podcast host</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
